--- a/data/trans_orig/P1413-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2007</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44395</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>26237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48474</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55933</t>
+          <t>55756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85501</t>
+          <t>85734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228615</t>
+          <t>228330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249975</t>
+          <t>249277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212364</t>
+          <t>211806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234939</t>
+          <t>234601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448347</t>
+          <t>448114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477915</t>
+          <t>478092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>90360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125452</t>
+          <t>126006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>148078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186707</t>
+          <t>190815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>248319</t>
+          <t>248173</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302180</t>
+          <t>304388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367623</t>
+          <t>367069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403049</t>
+          <t>402715</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317242</t>
+          <t>313134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357958</t>
+          <t>355871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694844</t>
+          <t>692636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748705</t>
+          <t>748851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37990</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>36806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61582</t>
+          <t>60991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59771</t>
+          <t>59098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94376</t>
+          <t>90887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280856</t>
+          <t>280618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273830</t>
+          <t>274421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298572</t>
+          <t>298606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>559882</t>
+          <t>563371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>594487</t>
+          <t>595160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54846</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84930</t>
+          <t>84096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37624</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63713</t>
+          <t>62977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97954</t>
+          <t>98794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138855</t>
+          <t>139847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273741</t>
+          <t>274575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303825</t>
+          <t>302251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>307743</t>
+          <t>308479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333832</t>
+          <t>333439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>590280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632173</t>
+          <t>631333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39973</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54616</t>
+          <t>55782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183910</t>
+          <t>183532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197173</t>
+          <t>196689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167695</t>
+          <t>168344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187209</t>
+          <t>188698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356360</t>
+          <t>355194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381831</t>
+          <t>380922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>25952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48797</t>
+          <t>47227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31313</t>
+          <t>31479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55866</t>
+          <t>55602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>63759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96770</t>
+          <t>95707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222014</t>
+          <t>223584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244581</t>
+          <t>244859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222278</t>
+          <t>222542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246831</t>
+          <t>246665</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>452185</t>
+          <t>453248</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485295</t>
+          <t>485196</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76933</t>
+          <t>76406</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111649</t>
+          <t>110512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74085</t>
+          <t>73610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109373</t>
+          <t>107697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>158628</t>
+          <t>157882</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207714</t>
+          <t>208188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>503378</t>
+          <t>504515</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>538094</t>
+          <t>538621</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>528846</t>
+          <t>530522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>564134</t>
+          <t>564609</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1045532</t>
+          <t>1045058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1094618</t>
+          <t>1095364</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134217</t>
+          <t>132892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178440</t>
+          <t>178692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165066</t>
+          <t>164735</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216023</t>
+          <t>214062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>313294</t>
+          <t>309307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>377901</t>
+          <t>373315</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>565355</t>
+          <t>565103</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>609578</t>
+          <t>610903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567488</t>
+          <t>569449</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>618445</t>
+          <t>618776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1149405</t>
+          <t>1153991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1214012</t>
+          <t>1217999</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>485131</t>
+          <t>491205</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>571871</t>
+          <t>571470</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>604265</t>
+          <t>602194</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>696767</t>
+          <t>692257</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1109635</t>
+          <t>1123590</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1242998</t>
+          <t>1242838</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2704672</t>
+          <t>2705073</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2791412</t>
+          <t>2785338</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2682430</t>
+          <t>2686940</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2774932</t>
+          <t>2777003</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5412743</t>
+          <t>5412903</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5546106</t>
+          <t>5532151</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2012</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>26927</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>49651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79185</t>
+          <t>79223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64373</t>
+          <t>64377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101689</t>
+          <t>100272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266860</t>
+          <t>267811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284233</t>
+          <t>284704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208060</t>
+          <t>208022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238774</t>
+          <t>237594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480294</t>
+          <t>481711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>517610</t>
+          <t>517606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42873</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51095</t>
+          <t>50989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82475</t>
+          <t>82194</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74998</t>
+          <t>74191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114810</t>
+          <t>113429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462654</t>
+          <t>464414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486327</t>
+          <t>487180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441290</t>
+          <t>441571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>472670</t>
+          <t>472776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914482</t>
+          <t>915863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954294</t>
+          <t>955101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36200</t>
+          <t>34484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36754</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64511</t>
+          <t>65326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58969</t>
+          <t>59308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92259</t>
+          <t>92258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287846</t>
+          <t>289562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308956</t>
+          <t>308854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276509</t>
+          <t>275694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>304266</t>
+          <t>302646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572807</t>
+          <t>572808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>606097</t>
+          <t>605758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49858</t>
+          <t>50174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65946</t>
+          <t>66058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96952</t>
+          <t>97362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138289</t>
+          <t>140036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324124</t>
+          <t>323808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348658</t>
+          <t>349253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291712</t>
+          <t>291312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323005</t>
+          <t>322893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>624644</t>
+          <t>622897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>665981</t>
+          <t>665571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43308</t>
+          <t>43219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56693</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85263</t>
+          <t>84436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84356</t>
+          <t>83723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120432</t>
+          <t>120291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169310</t>
+          <t>169399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191695</t>
+          <t>190698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134328</t>
+          <t>135155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162898</t>
+          <t>161877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>311777</t>
+          <t>311918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>347853</t>
+          <t>348486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>37337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64522</t>
+          <t>64019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69719</t>
+          <t>70742</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105596</t>
+          <t>105453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223774</t>
+          <t>223919</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246486</t>
+          <t>247289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213574</t>
+          <t>214077</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239641</t>
+          <t>240759</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446481</t>
+          <t>446624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482358</t>
+          <t>481335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55386</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87707</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119687</t>
+          <t>120467</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162644</t>
+          <t>164717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183469</t>
+          <t>185439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>239785</t>
+          <t>242407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>575081</t>
+          <t>573878</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607402</t>
+          <t>607439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>531209</t>
+          <t>529136</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>574166</t>
+          <t>573386</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1116856</t>
+          <t>1114234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1173172</t>
+          <t>1171202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79372</t>
+          <t>82500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105556</t>
+          <t>105726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147380</t>
+          <t>146987</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162331</t>
+          <t>165164</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>214362</t>
+          <t>214982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699726</t>
+          <t>696598</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>732122</t>
+          <t>729735</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>675198</t>
+          <t>675591</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>717022</t>
+          <t>716852</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1387314</t>
+          <t>1386694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1439345</t>
+          <t>1436512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>278211</t>
+          <t>278887</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>345079</t>
+          <t>345582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>599713</t>
+          <t>602211</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>696141</t>
+          <t>694407</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>899865</t>
+          <t>896548</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1016775</t>
+          <t>1013551</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3081700</t>
+          <t>3081197</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3148568</t>
+          <t>3147892</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2858957</t>
+          <t>2860691</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2955385</t>
+          <t>2952887</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5965102</t>
+          <t>5968326</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6082012</t>
+          <t>6085329</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2016</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43127</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71703</t>
+          <t>71004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70029</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104349</t>
+          <t>102780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252999</t>
+          <t>252905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274552</t>
+          <t>274021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>217000</t>
+          <t>217699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245576</t>
+          <t>244958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>478115</t>
+          <t>479684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512435</t>
+          <t>515127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49559</t>
+          <t>51581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47331</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76756</t>
+          <t>75662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469121</t>
+          <t>468106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488036</t>
+          <t>487311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473525</t>
+          <t>471503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498235</t>
+          <t>497183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948903</t>
+          <t>949997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>978328</t>
+          <t>980521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64372</t>
+          <t>65850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59822</t>
+          <t>58108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92692</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284030</t>
+          <t>283938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302824</t>
+          <t>301937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271937</t>
+          <t>270459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298919</t>
+          <t>298819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>562182</t>
+          <t>562960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>595052</t>
+          <t>596766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41922</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>55463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88671</t>
+          <t>86884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81088</t>
+          <t>83248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118970</t>
+          <t>123102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328042</t>
+          <t>328107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349547</t>
+          <t>350520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298612</t>
+          <t>300399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>331090</t>
+          <t>331820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>638277</t>
+          <t>634145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>676159</t>
+          <t>673999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29558</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42413</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37449</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63753</t>
+          <t>64605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181663</t>
+          <t>181213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199239</t>
+          <t>199118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176174</t>
+          <t>175369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196977</t>
+          <t>196645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366055</t>
+          <t>365203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392359</t>
+          <t>391349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,82 +9109,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>31454</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>21542</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>45433</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>55668</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>41663</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>71464</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>13,33%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>31454</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>21570</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>43936</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>16,09%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>55668</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>42698</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>74587</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228059</t>
+          <t>227575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246946</t>
+          <t>246400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,82 +9222,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>86,49%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>241661</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>227682</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>251573</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>83,37%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>480570</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>464774</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>494575</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>86,67%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>241661</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>229179</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>251545</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>88,48%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>83,91%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>92,1%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>480570</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>461651</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>493540</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>86,09%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>47670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80356</t>
+          <t>77923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94738</t>
+          <t>94713</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134504</t>
+          <t>133170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>151705</t>
+          <t>150278</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>202732</t>
+          <t>204542</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576202</t>
+          <t>578635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609730</t>
+          <t>608888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>556790</t>
+          <t>558124</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>596556</t>
+          <t>596581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1145120</t>
+          <t>1143310</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1196147</t>
+          <t>1197574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52178</t>
+          <t>51219</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85584</t>
+          <t>82284</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84870</t>
+          <t>85109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>125553</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146505</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>198034</t>
+          <t>194865</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692999</t>
+          <t>696299</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726405</t>
+          <t>727364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>701861</t>
+          <t>700614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>741297</t>
+          <t>741058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1406716</t>
+          <t>1409885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1458245</t>
+          <t>1460053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>245425</t>
+          <t>246051</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>315170</t>
+          <t>310896</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>444603</t>
+          <t>453078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>535404</t>
+          <t>541806</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>715865</t>
+          <t>716938</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>826964</t>
+          <t>823410</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3079180</t>
+          <t>3083454</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3148925</t>
+          <t>3148299</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3009138</t>
+          <t>3002736</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3099939</t>
+          <t>3091464</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6111928</t>
+          <t>6115482</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6223027</t>
+          <t>6221954</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2023</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43706</t>
+          <t>43713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42803</t>
+          <t>42698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54548</t>
+          <t>53832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80471</t>
+          <t>80722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267737</t>
+          <t>267730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288730</t>
+          <t>288652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246832</t>
+          <t>246937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263133</t>
+          <t>263063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520606</t>
+          <t>520355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546529</t>
+          <t>547245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59561</t>
+          <t>59459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102313</t>
+          <t>99648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139087</t>
+          <t>137560</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174759</t>
+          <t>172237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205739</t>
+          <t>205240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259142</t>
+          <t>262069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415080</t>
+          <t>417745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457832</t>
+          <t>457934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339532</t>
+          <t>342054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>375204</t>
+          <t>376731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772542</t>
+          <t>769615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825945</t>
+          <t>826444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75592</t>
+          <t>75753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87349</t>
+          <t>86483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114780</t>
+          <t>114231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142798</t>
+          <t>142700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179948</t>
+          <t>180628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>240458</t>
+          <t>240297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266352</t>
+          <t>266345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234348</t>
+          <t>234897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261779</t>
+          <t>262645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>485230</t>
+          <t>484550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>522380</t>
+          <t>522478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64597</t>
+          <t>63897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64101</t>
+          <t>68794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146084</t>
+          <t>146688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124148</t>
+          <t>119123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192757</t>
+          <t>194607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247960</t>
+          <t>248660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276789</t>
+          <t>276898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329634</t>
+          <t>329030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>411617</t>
+          <t>406924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>595517</t>
+          <t>593667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>664126</t>
+          <t>669151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>40004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>55176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64039</t>
+          <t>64815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>85851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141405</t>
+          <t>141873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156922</t>
+          <t>157425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152730</t>
+          <t>153098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169031</t>
+          <t>168270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300148</t>
+          <t>300405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322217</t>
+          <t>321441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58039</t>
+          <t>58152</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83478</t>
+          <t>83063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82241</t>
+          <t>81426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106424</t>
+          <t>104038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145690</t>
+          <t>147673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181279</t>
+          <t>181151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186158</t>
+          <t>186573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211597</t>
+          <t>211484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149963</t>
+          <t>152349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174146</t>
+          <t>174961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344744</t>
+          <t>344872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>380333</t>
+          <t>378350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141149</t>
+          <t>140694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186899</t>
+          <t>186869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>356547</t>
+          <t>358518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>684317</t>
+          <t>666591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>501983</t>
+          <t>501178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>909374</t>
+          <t>947229</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>433288</t>
+          <t>433318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>479038</t>
+          <t>479493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164142</t>
+          <t>181868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>491912</t>
+          <t>489941</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>559272</t>
+          <t>521417</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>966663</t>
+          <t>967468</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54407</t>
+          <t>56379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176875</t>
+          <t>177243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186245</t>
+          <t>186436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>228603</t>
+          <t>228152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>204497</t>
+          <t>204518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>395627</t>
+          <t>398206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>751845</t>
+          <t>751477</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>874313</t>
+          <t>872341</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>486789</t>
+          <t>487240</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>529147</t>
+          <t>528956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1248485</t>
+          <t>1245906</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1439615</t>
+          <t>1439594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>477330</t>
+          <t>465913</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>669457</t>
+          <t>668553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1071397</t>
+          <t>1069708</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1691433</t>
+          <t>1662016</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1638912</t>
+          <t>1629138</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2431812</t>
+          <t>2479075</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2784511</t>
+          <t>2785415</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2976638</t>
+          <t>2988055</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1965849</t>
+          <t>1995266</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2585885</t>
+          <t>2587574</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4679438</t>
+          <t>4632175</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5472338</t>
+          <t>5482112</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1413-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44680</t>
+          <t>44849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49032</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85734</t>
+          <t>84717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228330</t>
+          <t>228161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249277</t>
+          <t>249283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>211806</t>
+          <t>212365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234601</t>
+          <t>233886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448114</t>
+          <t>449131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>478092</t>
+          <t>478966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90360</t>
+          <t>90248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126006</t>
+          <t>126177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148078</t>
+          <t>145359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190815</t>
+          <t>187509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>248173</t>
+          <t>245066</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>304388</t>
+          <t>302843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367069</t>
+          <t>366898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402715</t>
+          <t>402827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313134</t>
+          <t>316440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355871</t>
+          <t>358590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692636</t>
+          <t>694181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748851</t>
+          <t>751958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>36098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60991</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59098</t>
+          <t>59215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90887</t>
+          <t>93292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280618</t>
+          <t>280777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300719</t>
+          <t>301060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274421</t>
+          <t>274734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298606</t>
+          <t>299314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>563371</t>
+          <t>560966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>595160</t>
+          <t>595043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>54543</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>85145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>38998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62977</t>
+          <t>64221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98794</t>
+          <t>100129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139847</t>
+          <t>138553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274575</t>
+          <t>273526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302251</t>
+          <t>304128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>308479</t>
+          <t>307235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333439</t>
+          <t>332458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>590280</t>
+          <t>591574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>631333</t>
+          <t>629998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>40918</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30054</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55782</t>
+          <t>53353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183532</t>
+          <t>182967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196689</t>
+          <t>196614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168344</t>
+          <t>166750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188698</t>
+          <t>187146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355194</t>
+          <t>357623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>380922</t>
+          <t>382593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>47919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>55633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63759</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95707</t>
+          <t>96719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223584</t>
+          <t>222892</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244859</t>
+          <t>244744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222542</t>
+          <t>222511</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246665</t>
+          <t>247207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>453248</t>
+          <t>452236</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485196</t>
+          <t>485543</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76406</t>
+          <t>77358</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110512</t>
+          <t>111009</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73610</t>
+          <t>72567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107697</t>
+          <t>106533</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157882</t>
+          <t>156824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208188</t>
+          <t>206118</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>504515</t>
+          <t>504018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>538621</t>
+          <t>537669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>530522</t>
+          <t>531686</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>564609</t>
+          <t>565652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1045058</t>
+          <t>1047128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1095364</t>
+          <t>1096422</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132892</t>
+          <t>134974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178692</t>
+          <t>179443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164735</t>
+          <t>163389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>214062</t>
+          <t>211633</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>309307</t>
+          <t>307975</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>373315</t>
+          <t>373073</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>565103</t>
+          <t>564352</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610903</t>
+          <t>608821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>569449</t>
+          <t>571878</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>618776</t>
+          <t>620122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1153991</t>
+          <t>1154233</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1217999</t>
+          <t>1219331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>491205</t>
+          <t>491274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>571470</t>
+          <t>578124</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>602194</t>
+          <t>601826</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>692257</t>
+          <t>696772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1123590</t>
+          <t>1116665</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1242838</t>
+          <t>1239970</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2705073</t>
+          <t>2698419</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2785338</t>
+          <t>2785269</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2686940</t>
+          <t>2682425</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2777003</t>
+          <t>2777371</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5412903</t>
+          <t>5415771</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5532151</t>
+          <t>5539076</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49651</t>
+          <t>48250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79223</t>
+          <t>79068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64377</t>
+          <t>63525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100272</t>
+          <t>99419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267811</t>
+          <t>268027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284704</t>
+          <t>284129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208022</t>
+          <t>208177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237594</t>
+          <t>238995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>481711</t>
+          <t>482564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>517606</t>
+          <t>518458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18347</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41113</t>
+          <t>42036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50989</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82194</t>
+          <t>81822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74191</t>
+          <t>74130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113429</t>
+          <t>112097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>464414</t>
+          <t>463491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487180</t>
+          <t>486709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441571</t>
+          <t>441943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>472776</t>
+          <t>472853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915863</t>
+          <t>917195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>955101</t>
+          <t>955162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>37722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65326</t>
+          <t>64688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,47 +4792,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>18,97%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>74825</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>59186</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>94472</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>11,25%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>74825</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>59308</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>92258</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289562</t>
+          <t>288507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308854</t>
+          <t>308031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275694</t>
+          <t>276332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302646</t>
+          <t>303298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,47 +4905,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>88,94%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>590241</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>570594</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>605880</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>88,75%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>590241</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>572808</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>605758</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,75%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>25935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>50434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66058</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>97392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97362</t>
+          <t>98281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140036</t>
+          <t>139268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>323808</t>
+          <t>323548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349253</t>
+          <t>348047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291312</t>
+          <t>291559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322893</t>
+          <t>322793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>622897</t>
+          <t>623665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>665571</t>
+          <t>664652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>43729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57714</t>
+          <t>57113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84436</t>
+          <t>84701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83723</t>
+          <t>84353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120291</t>
+          <t>121039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169399</t>
+          <t>168889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190698</t>
+          <t>190527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135155</t>
+          <t>134890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161877</t>
+          <t>162478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>311918</t>
+          <t>311170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>348486</t>
+          <t>347856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>26688</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>50312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>62769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70742</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105453</t>
+          <t>107084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223919</t>
+          <t>223669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247289</t>
+          <t>247293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214077</t>
+          <t>215327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240759</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446624</t>
+          <t>444993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481335</t>
+          <t>480425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>55305</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>87764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120467</t>
+          <t>121031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164717</t>
+          <t>163817</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>185439</t>
+          <t>184533</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242407</t>
+          <t>241737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>573878</t>
+          <t>575024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607439</t>
+          <t>607483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>529136</t>
+          <t>530036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>573386</t>
+          <t>572822</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1114234</t>
+          <t>1114904</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1171202</t>
+          <t>1172108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>49467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82500</t>
+          <t>82202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>104340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146987</t>
+          <t>146611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>165164</t>
+          <t>163950</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>214982</t>
+          <t>215893</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>696598</t>
+          <t>696896</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>729735</t>
+          <t>729631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>675591</t>
+          <t>675967</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>716852</t>
+          <t>718238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1386694</t>
+          <t>1385783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1436512</t>
+          <t>1437726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>278887</t>
+          <t>272492</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>345582</t>
+          <t>346774</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>602211</t>
+          <t>599804</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>694407</t>
+          <t>695235</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>896548</t>
+          <t>895592</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1013551</t>
+          <t>1019284</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3081197</t>
+          <t>3080005</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3147892</t>
+          <t>3154287</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2860691</t>
+          <t>2859863</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2952887</t>
+          <t>2955294</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5968326</t>
+          <t>5962593</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6085329</t>
+          <t>6086285</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>41069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>43807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>71663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67337</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102780</t>
+          <t>103313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252905</t>
+          <t>252692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274021</t>
+          <t>274252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>217699</t>
+          <t>217040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244958</t>
+          <t>244896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479684</t>
+          <t>479151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515127</t>
+          <t>513582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>34278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>25495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51581</t>
+          <t>50581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>44879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75662</t>
+          <t>74067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468106</t>
+          <t>468297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487311</t>
+          <t>486749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471503</t>
+          <t>472503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497183</t>
+          <t>497589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>949997</t>
+          <t>951592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>980521</t>
+          <t>980780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37490</t>
+          <t>38068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65850</t>
+          <t>66683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58108</t>
+          <t>58637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91914</t>
+          <t>92070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283938</t>
+          <t>283767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301937</t>
+          <t>302309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270459</t>
+          <t>269626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298819</t>
+          <t>298241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>562960</t>
+          <t>562804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>596766</t>
+          <t>596237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41857</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55463</t>
+          <t>55727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86884</t>
+          <t>86611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83248</t>
+          <t>82395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123102</t>
+          <t>121116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328107</t>
+          <t>327854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>350520</t>
+          <t>350142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300399</t>
+          <t>300672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>331820</t>
+          <t>331556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634145</t>
+          <t>636131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673999</t>
+          <t>674852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>27803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43218</t>
+          <t>42279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>38574</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64605</t>
+          <t>65914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181213</t>
+          <t>183418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199118</t>
+          <t>199016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175369</t>
+          <t>176308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196645</t>
+          <t>197094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365203</t>
+          <t>363894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391349</t>
+          <t>391234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>35636</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45433</t>
+          <t>43787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>41977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71464</t>
+          <t>72131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227575</t>
+          <t>227487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246400</t>
+          <t>247551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227682</t>
+          <t>229328</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251573</t>
+          <t>251202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>464774</t>
+          <t>464107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494575</t>
+          <t>494261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47670</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77923</t>
+          <t>79184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94713</t>
+          <t>94493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133170</t>
+          <t>132937</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150278</t>
+          <t>150035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204542</t>
+          <t>198531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>578635</t>
+          <t>577374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608888</t>
+          <t>609168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>558124</t>
+          <t>558357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>596581</t>
+          <t>596801</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1143310</t>
+          <t>1149321</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1197574</t>
+          <t>1197817</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51219</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82284</t>
+          <t>82949</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85109</t>
+          <t>85184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>126863</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144697</t>
+          <t>145503</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>194865</t>
+          <t>196386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>696299</t>
+          <t>695634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727364</t>
+          <t>727580</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>700614</t>
+          <t>699304</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>741058</t>
+          <t>740983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1409885</t>
+          <t>1408364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1460053</t>
+          <t>1459247</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>246051</t>
+          <t>245974</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>310896</t>
+          <t>309842</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>453078</t>
+          <t>451864</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>541806</t>
+          <t>539195</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>716938</t>
+          <t>721383</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>823410</t>
+          <t>829037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3083454</t>
+          <t>3084508</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3148299</t>
+          <t>3148376</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3002736</t>
+          <t>3005347</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3091464</t>
+          <t>3092678</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6115482</t>
+          <t>6109855</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6221954</t>
+          <t>6217509</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>45375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42698</t>
+          <t>45135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>69489</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80722</t>
+          <t>83376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>280243</t>
+          <t>285703</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267730</t>
+          <t>273470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288652</t>
+          <t>294738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>255455</t>
+          <t>279714</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246937</t>
+          <t>270926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263063</t>
+          <t>287141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>535697</t>
+          <t>565417</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520355</t>
+          <t>551530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>547245</t>
+          <t>577735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>80483</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59459</t>
+          <t>60371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99648</t>
+          <t>98798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>155235</t>
+          <t>161982</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137560</t>
+          <t>145056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172237</t>
+          <t>182073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>231978</t>
+          <t>242465</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205240</t>
+          <t>216007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262069</t>
+          <t>270559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>440650</t>
+          <t>449177</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417745</t>
+          <t>430862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457934</t>
+          <t>469289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>359056</t>
+          <t>383827</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342054</t>
+          <t>363736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376731</t>
+          <t>400753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>799706</t>
+          <t>833004</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>769615</t>
+          <t>804910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>826444</t>
+          <t>859462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>61146</t>
+          <t>61447</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49705</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75753</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99333</t>
+          <t>101679</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86483</t>
+          <t>89620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114231</t>
+          <t>115511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>160479</t>
+          <t>163126</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142700</t>
+          <t>145911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180628</t>
+          <t>181630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>254904</t>
+          <t>254546</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>240297</t>
+          <t>240743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266345</t>
+          <t>265838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>249795</t>
+          <t>254702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234897</t>
+          <t>240870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262645</t>
+          <t>266761</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>504699</t>
+          <t>509249</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>484550</t>
+          <t>490745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>522478</t>
+          <t>526464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48289</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63897</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>114716</t>
+          <t>125525</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68794</t>
+          <t>109802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146688</t>
+          <t>144244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>163006</t>
+          <t>177088</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119123</t>
+          <t>154518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194607</t>
+          <t>199358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>264268</t>
+          <t>321582</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248660</t>
+          <t>305276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276898</t>
+          <t>334637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>361002</t>
+          <t>296436</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329030</t>
+          <t>277717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>406924</t>
+          <t>312159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>625268</t>
+          <t>618019</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>593667</t>
+          <t>595749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>669151</t>
+          <t>640589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>40907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40004</t>
+          <t>43265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55176</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>81780</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64815</t>
+          <t>70198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85851</t>
+          <t>94537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>150281</t>
+          <t>173736</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141873</t>
+          <t>163866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157425</t>
+          <t>181389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>160824</t>
+          <t>176080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153098</t>
+          <t>167458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168270</t>
+          <t>183558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>311105</t>
+          <t>349817</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300405</t>
+          <t>337060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>321441</t>
+          <t>361399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>177982</t>
+          <t>204773</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177982</t>
+          <t>204773</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177982</t>
+          <t>204773</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386256</t>
+          <t>431597</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386256</t>
+          <t>431597</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386256</t>
+          <t>431597</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,102 +12412,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>70491</t>
+          <t>69215</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58152</t>
+          <t>57494</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83063</t>
+          <t>80509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>95248</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>82693</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>106317</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>40,41%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>164462</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>147433</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>180562</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>30,81%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>93127</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>81426</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>104038</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>36,32%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>40,58%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>163618</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>147673</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>181151</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>31,1%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -12525,102 +12525,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>199145</t>
+          <t>201492</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186573</t>
+          <t>190198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211484</t>
+          <t>213213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>70,26%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>78,76%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>167851</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>156782</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>180406</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>63,8%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>59,59%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>68,57%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>369344</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>353244</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>386373</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>69,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>78,43%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>163260</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>152349</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>174961</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>59,42%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>68,24%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>362405</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>344872</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>378350</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>68,9%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>162765</t>
+          <t>187323</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140694</t>
+          <t>162189</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186869</t>
+          <t>210981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>484036</t>
+          <t>336913</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>358518</t>
+          <t>309890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>666591</t>
+          <t>360957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>646801</t>
+          <t>524236</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>501178</t>
+          <t>488107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>947229</t>
+          <t>564852</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>457422</t>
+          <t>527879</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>433318</t>
+          <t>504221</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>479493</t>
+          <t>553013</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>364423</t>
+          <t>433770</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181868</t>
+          <t>409726</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>489941</t>
+          <t>460793</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>821845</t>
+          <t>961649</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>521417</t>
+          <t>921033</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>967468</t>
+          <t>997778</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>620187</t>
+          <t>715202</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620187</t>
+          <t>715202</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>620187</t>
+          <t>715202</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848459</t>
+          <t>770683</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848459</t>
+          <t>770683</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848459</t>
+          <t>770683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1468646</t>
+          <t>1485885</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1468646</t>
+          <t>1485885</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1468646</t>
+          <t>1485885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>123725</t>
+          <t>140067</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56379</t>
+          <t>121278</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177243</t>
+          <t>162298</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>205586</t>
+          <t>233499</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186436</t>
+          <t>209580</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>228152</t>
+          <t>256333</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>329311</t>
+          <t>373566</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>204518</t>
+          <t>342280</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398206</t>
+          <t>405802</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>804995</t>
+          <t>658005</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>751477</t>
+          <t>635774</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>872341</t>
+          <t>676794</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>509806</t>
+          <t>597110</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>487240</t>
+          <t>574276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>528956</t>
+          <t>621029</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1314801</t>
+          <t>1255115</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1245906</t>
+          <t>1222879</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1439594</t>
+          <t>1286401</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>602060</t>
+          <t>654276</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>465913</t>
+          <t>607107</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>668553</t>
+          <t>705157</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1233663</t>
+          <t>1141936</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1069708</t>
+          <t>1093870</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1662016</t>
+          <t>1190892</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1835724</t>
+          <t>1796212</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1629138</t>
+          <t>1731327</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2479075</t>
+          <t>1860958</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2851908</t>
+          <t>2872122</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2785415</t>
+          <t>2821241</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2988055</t>
+          <t>2919291</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2423619</t>
+          <t>2589492</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1995266</t>
+          <t>2540536</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2587574</t>
+          <t>2637558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5275526</t>
+          <t>5461614</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4632175</t>
+          <t>5396868</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5482112</t>
+          <t>5526499</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
